--- a/CodeSystem-not-medication-reason-cs.xlsx
+++ b/CodeSystem-not-medication-reason-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T11:15:53+00:00</t>
+    <t>2026-05-08T09:03:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-not-medication-reason-cs.xlsx
+++ b/CodeSystem-not-medication-reason-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:03:17+00:00</t>
+    <t>2026-05-08T09:31:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-not-medication-reason-cs.xlsx
+++ b/CodeSystem-not-medication-reason-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:31:23+00:00</t>
+    <t>2026-05-08T10:13:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-not-medication-reason-cs.xlsx
+++ b/CodeSystem-not-medication-reason-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T10:13:17+00:00</t>
+    <t>2026-05-11T15:54:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-not-medication-reason-cs.xlsx
+++ b/CodeSystem-not-medication-reason-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:34+00:00</t>
+    <t>2026-05-11T15:54:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-not-medication-reason-cs.xlsx
+++ b/CodeSystem-not-medication-reason-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:44+00:00</t>
+    <t>2026-05-12T07:59:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-not-medication-reason-cs.xlsx
+++ b/CodeSystem-not-medication-reason-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T07:59:38+00:00</t>
+    <t>2026-05-12T09:41:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-not-medication-reason-cs.xlsx
+++ b/CodeSystem-not-medication-reason-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T09:41:56+00:00</t>
+    <t>2026-05-12T11:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-not-medication-reason-cs.xlsx
+++ b/CodeSystem-not-medication-reason-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T11:55:23+00:00</t>
+    <t>2026-05-13T14:14:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-not-medication-reason-cs.xlsx
+++ b/CodeSystem-not-medication-reason-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:14:43+00:00</t>
+    <t>2026-05-13T15:23:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-not-medication-reason-cs.xlsx
+++ b/CodeSystem-not-medication-reason-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T15:23:44+00:00</t>
+    <t>2026-05-14T08:09:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-not-medication-reason-cs.xlsx
+++ b/CodeSystem-not-medication-reason-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:09:55+00:00</t>
+    <t>2026-05-14T08:55:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-not-medication-reason-cs.xlsx
+++ b/CodeSystem-not-medication-reason-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:55:50+00:00</t>
+    <t>2026-05-14T09:35:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-not-medication-reason-cs.xlsx
+++ b/CodeSystem-not-medication-reason-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T09:35:04+00:00</t>
+    <t>2026-05-14T11:02:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-not-medication-reason-cs.xlsx
+++ b/CodeSystem-not-medication-reason-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T11:02:20+00:00</t>
+    <t>2026-05-15T10:10:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-not-medication-reason-cs.xlsx
+++ b/CodeSystem-not-medication-reason-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T10:10:20+00:00</t>
+    <t>2026-06-01T07:47:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-not-medication-reason-cs.xlsx
+++ b/CodeSystem-not-medication-reason-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T07:47:29+00:00</t>
+    <t>2026-06-01T10:24:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-not-medication-reason-cs.xlsx
+++ b/CodeSystem-not-medication-reason-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:24:12+00:00</t>
+    <t>2026-06-01T10:42:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-not-medication-reason-cs.xlsx
+++ b/CodeSystem-not-medication-reason-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:42:50+00:00</t>
+    <t>2026-06-01T12:57:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-not-medication-reason-cs.xlsx
+++ b/CodeSystem-not-medication-reason-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T12:57:35+00:00</t>
+    <t>2026-06-02T10:42:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-not-medication-reason-cs.xlsx
+++ b/CodeSystem-not-medication-reason-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T10:42:43+00:00</t>
+    <t>2026-06-03T07:55:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-not-medication-reason-cs.xlsx
+++ b/CodeSystem-not-medication-reason-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T07:55:03+00:00</t>
+    <t>2026-06-03T14:48:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-not-medication-reason-cs.xlsx
+++ b/CodeSystem-not-medication-reason-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:48:08+00:00</t>
+    <t>2026-06-03T14:50:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-not-medication-reason-cs.xlsx
+++ b/CodeSystem-not-medication-reason-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:50:23+00:00</t>
+    <t>2026-06-08T09:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-not-medication-reason-cs.xlsx
+++ b/CodeSystem-not-medication-reason-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T09:55:23+00:00</t>
+    <t>2026-06-08T10:51:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-not-medication-reason-cs.xlsx
+++ b/CodeSystem-not-medication-reason-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T10:51:55+00:00</t>
+    <t>2026-06-08T11:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-not-medication-reason-cs.xlsx
+++ b/CodeSystem-not-medication-reason-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T11:21:15+00:00</t>
+    <t>2026-06-11T11:47:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-not-medication-reason-cs.xlsx
+++ b/CodeSystem-not-medication-reason-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T11:47:40+00:00</t>
+    <t>2026-06-11T14:44:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-not-medication-reason-cs.xlsx
+++ b/CodeSystem-not-medication-reason-cs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="57">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:44:28+00:00</t>
+    <t>2026-06-12T09:34:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -142,6 +142,9 @@
   </si>
   <si>
     <t>Patient or family did not consent</t>
+  </si>
+  <si>
+    <t>Cost-of-drug</t>
   </si>
   <si>
     <t>Cost of drug</t>
@@ -527,7 +530,7 @@
         <v>43</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D3" s="2"/>
     </row>
@@ -536,10 +539,10 @@
         <v>40</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D4" s="2"/>
     </row>
@@ -548,10 +551,10 @@
         <v>40</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D5" s="2"/>
     </row>
@@ -560,10 +563,10 @@
         <v>40</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D6" s="2"/>
     </row>
@@ -572,10 +575,10 @@
         <v>40</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D7" s="2"/>
     </row>
@@ -584,10 +587,10 @@
         <v>40</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D8" s="2"/>
     </row>
@@ -596,10 +599,10 @@
         <v>40</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D9" s="2"/>
     </row>

--- a/CodeSystem-not-medication-reason-cs.xlsx
+++ b/CodeSystem-not-medication-reason-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T09:34:13+00:00</t>
+    <t>2026-07-01T13:43:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-not-medication-reason-cs.xlsx
+++ b/CodeSystem-not-medication-reason-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T13:43:23+00:00</t>
+    <t>2026-07-09T09:09:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-not-medication-reason-cs.xlsx
+++ b/CodeSystem-not-medication-reason-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:09:43+00:00</t>
+    <t>2026-07-13T09:21:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-not-medication-reason-cs.xlsx
+++ b/CodeSystem-not-medication-reason-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:21:26+00:00</t>
+    <t>2026-07-13T09:30:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-not-medication-reason-cs.xlsx
+++ b/CodeSystem-not-medication-reason-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:30:27+00:00</t>
+    <t>2026-07-14T07:23:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-not-medication-reason-cs.xlsx
+++ b/CodeSystem-not-medication-reason-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T07:23:58+00:00</t>
+    <t>2026-07-17T09:40:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-not-medication-reason-cs.xlsx
+++ b/CodeSystem-not-medication-reason-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T09:40:30+00:00</t>
+    <t>2026-07-21T08:04:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -174,7 +174,7 @@
     <t>Patient did not use anticoagulant before ICH (forgot to take a pill)</t>
   </si>
   <si>
-    <t>Not-Reported</t>
+    <t>not-reported</t>
   </si>
   <si>
     <t>Reason for not giving anticoagulant reversal not reported</t>

--- a/CodeSystem-not-medication-reason-cs.xlsx
+++ b/CodeSystem-not-medication-reason-cs.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/CodeSystem/not-medication-reason-cs</t>
+    <t>http://qualityregistry.org/CodeSystem/not-medication-reason-cs</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:04:16+00:00</t>
+    <t>2026-08-31T09:17:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Tecnomod / Universidad de Murcia (http://tecnomod-um.org)</t>
+    <t>Tecnomod / Universidad de Murcia (http://qualityregistry.org)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Local RESQ stroke registry CodeSystem generated from enum_models.py for system http://tecnomod-um.org/CodeSystem/not-medication-reason-cs.</t>
+    <t>Local RESQ stroke registry CodeSystem generated from enum_models.py for system http://qualityregistry.org/CodeSystem/not-medication-reason-cs.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/CodeSystem-not-medication-reason-cs.xlsx
+++ b/CodeSystem-not-medication-reason-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T09:17:06+00:00</t>
+    <t>2026-08-31T10:08:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-not-medication-reason-cs.xlsx
+++ b/CodeSystem-not-medication-reason-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T10:08:26+00:00</t>
+    <t>2026-09-04T09:44:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/CodeSystem-not-medication-reason-cs.xlsx
+++ b/CodeSystem-not-medication-reason-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:44:50+00:00</t>
+    <t>2026-09-04T10:11:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
